--- a/Calendario Data Engineer V1.xlsx
+++ b/Calendario Data Engineer V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\diplomado-data-engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67048B3F-DF0F-4C9C-A14F-B4A100D8CE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8856C1E2-3C04-4A35-BAC4-2DAB283D341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>Programa Diplomado
 Data Engineer versión 1 - 2026</t>
@@ -1962,6 +1962,9 @@
       <c r="D46" s="3">
         <v>3</v>
       </c>
+      <c r="E46" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
@@ -1976,6 +1979,9 @@
       <c r="D47" s="3">
         <v>3</v>
       </c>
+      <c r="E47" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
@@ -1989,6 +1995,9 @@
       </c>
       <c r="D48" s="3">
         <v>3</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
@@ -2228,11 +2237,11 @@
       </c>
       <c r="E66">
         <f>SUMIF(E4:E63,"ok",D4:D63)</f>
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F66" s="27">
         <f>+E66/D66</f>
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">

--- a/Calendario Data Engineer V1.xlsx
+++ b/Calendario Data Engineer V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\diplomado-data-engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8856C1E2-3C04-4A35-BAC4-2DAB283D341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3597CC-E233-4006-9025-7C6447F6DD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
+    <workbookView xWindow="28680" yWindow="-2355" windowWidth="29040" windowHeight="15720" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/Calendario Data Engineer V1.xlsx
+++ b/Calendario Data Engineer V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\diplomado-data-engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3597CC-E233-4006-9025-7C6447F6DD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA958361-1B64-436F-A948-74EDFFCF4B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2355" windowWidth="29040" windowHeight="15720" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
   <si>
     <t>Programa Diplomado
 Data Engineer versión 1 - 2026</t>
@@ -2013,6 +2013,9 @@
       <c r="D49" s="3">
         <v>3</v>
       </c>
+      <c r="E49" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
@@ -2026,6 +2029,9 @@
       </c>
       <c r="D50" s="3">
         <v>3</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2052,6 +2058,9 @@
       <c r="D52" s="3">
         <v>3</v>
       </c>
+      <c r="E52" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
@@ -2066,6 +2075,9 @@
       <c r="D53" s="3">
         <v>3</v>
       </c>
+      <c r="E53" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
@@ -2080,6 +2092,9 @@
       <c r="D54" s="3">
         <v>3</v>
       </c>
+      <c r="E54" s="20" t="s">
+        <v>76</v>
+      </c>
       <c r="M54" s="1"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
@@ -2095,6 +2110,9 @@
       <c r="D55" s="3">
         <v>3</v>
       </c>
+      <c r="E55" s="20" t="s">
+        <v>76</v>
+      </c>
       <c r="M55" s="1"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
@@ -2110,6 +2128,9 @@
       <c r="D56" s="3">
         <v>3</v>
       </c>
+      <c r="E56" s="20" t="s">
+        <v>76</v>
+      </c>
       <c r="M56" s="1"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
@@ -2124,6 +2145,9 @@
       </c>
       <c r="D57" s="3">
         <v>3</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>76</v>
       </c>
       <c r="M57" s="1"/>
     </row>
@@ -2144,13 +2168,16 @@
         <v>46</v>
       </c>
       <c r="B59" s="19">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>45</v>
       </c>
       <c r="D59" s="3">
         <v>3</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
@@ -2158,7 +2185,7 @@
         <v>47</v>
       </c>
       <c r="B60" s="19">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>46</v>
@@ -2172,7 +2199,7 @@
         <v>48</v>
       </c>
       <c r="B61" s="19">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>47</v>
@@ -2186,7 +2213,7 @@
         <v>49</v>
       </c>
       <c r="B62" s="19">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>48</v>
@@ -2199,8 +2226,8 @@
       <c r="A63" s="4">
         <v>50</v>
       </c>
-      <c r="B63" s="19">
-        <v>46232</v>
+      <c r="B63" s="1">
+        <v>46234</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>49</v>
@@ -2237,11 +2264,11 @@
       </c>
       <c r="E66">
         <f>SUMIF(E4:E63,"ok",D4:D63)</f>
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="F66" s="27">
         <f>+E66/D66</f>
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">

--- a/Calendario Data Engineer V1.xlsx
+++ b/Calendario Data Engineer V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\diplomado-data-engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA958361-1B64-436F-A948-74EDFFCF4B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B51273-CDF0-4CF3-8DD2-781565598FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5F69A3EF-6077-4BDE-A151-51A314216C0C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="77">
   <si>
     <t>Programa Diplomado
 Data Engineer versión 1 - 2026</t>
@@ -2193,6 +2193,9 @@
       <c r="D60" s="3">
         <v>3</v>
       </c>
+      <c r="E60" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
@@ -2264,11 +2267,11 @@
       </c>
       <c r="E66">
         <f>SUMIF(E4:E63,"ok",D4:D63)</f>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F66" s="27">
         <f>+E66/D66</f>
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
